--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221032</v>
       </c>
       <c r="B2" t="n">
-        <v>92285</v>
+        <v>92440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125221031</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92442</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221032</v>
+        <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665841</v>
+        <v>665884</v>
       </c>
       <c r="R2" t="n">
-        <v>7203176</v>
+        <v>7203189</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221031</v>
+        <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92442</v>
+        <v>92440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665884</v>
+        <v>665841</v>
       </c>
       <c r="R3" t="n">
-        <v>7203189</v>
+        <v>7203176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92504</v>
+        <v>92512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22360-2025 artfynd.xlsx
+++ b/artfynd/A 22360-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221031</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221032</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
